--- a/final_outputs.xlsx
+++ b/final_outputs.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>Utcahasználat (jelenleg) - Közlekedési élmények</t>
+          <t>Utcahasználat (jelenleg) - Közlekedés</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>Utcahasználat (jelenleg) - Közlekedési élmények</t>
+          <t>Utcahasználat (jelenleg) - Közlekedés</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -19640,7 +19640,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -21492,7 +21492,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -22053,7 +22053,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -26654,7 +26654,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
@@ -27913,7 +27913,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
@@ -28404,7 +28404,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
@@ -28572,7 +28572,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>fiatal bérlő</t>
+          <t>fiatalabb bérlő</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>fiatal tulajdonos</t>
+          <t>fiatalabb tulajdonos</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
